--- a/Backend/utility/cdr_report/CDR_Pipelines/s4c2_cc_final.xlsx
+++ b/Backend/utility/cdr_report/CDR_Pipelines/s4c2_cc_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,22 +446,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Source Types</t>
+          <t>Source Type</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Evidence Count</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Image URLs</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Image Captions</t>
+          <t>Page Number</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -471,35 +471,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>critical</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>rules_passed</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rules_passed_count</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rule_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>reasoning</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>photo_no</t>
         </is>
@@ -508,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power Switch</t>
+          <t>Infinity MTx device</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Main Device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -528,58 +533,85 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 7]</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
+          <t>Exceptional performance – high cell viability and delivery efficiencies with decreased recovery and expansion times
+Simple, streamlined workflow —  easy to optimize and no need for cell concentration and buffer exchanges
+Operational and cell-friendly processing — no specific media, buffers, or chemical additives required
+Product Contents
+With the purchase of the Infinity MTx, CellFE provides the following products and accessories:
+System contents
+Optimizer kit contents
+Upon purchase of the Infinity MTx, users are asked to select an Optimizer Kit with sizes relevant to the cell types that will be used (see sizes below). Optimizer kits come with four MPAs. Once the desired MPA size is determined, users can purchase single-use MPAs of the correct size in packs of four. 
+Optimizer Kits
+System Components
+Infinity MTx device
+Front Panel
+User Interface Touchscreen – From here, the operator can detail and conduct the transfection processes, view and export information about previous transfection runs, change default system settings, and access additional information about operating the Infinity MTx. (See the software section of the manual for more information).
+Sample Loading Tray – Compatible with the Infinity MPA and Optimizer kit. Use the eject button on the touchscreen to open the tray. The MPA or Optimizer kit can be placed in the open tray by matching up the protrusion on the device with the recess on the tray.  WARNING:  Ensure nothing is touching the seam between the tray and the main body of the instrument, as this can damage the instrumentation and may cause harm to the user.
+Barcode Scanner – Located on the underside of the instrument above the tray. The barcode scanner reads the barcodes on the Infinity MPA package and saves device specific information to the notes section. Press the “Scan /Read ID” button to scan the barcode. 
+Back Panel
+Exhaust Air Vents – Used to vent air out of the instrument. CAUTION Do not block – Ensure at least 6” of clearan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Explicitly listed as a system component and the main device for operation.</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>[1, 3, 4, 8]</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Power switch is required by IEC 61010, is located in safety and hazardous circuitry, and is relied upon for safe abnormal operation (disconnection from mains).</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>The Infinity MTx device is the main system component required by the standard and controlling documents. It contains hazardous electrical and pneumatic circuitry, encloses these hazards, and any change or removal would result in loss of all safety functions and introduce multiple hazards.</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enclosure</t>
+          <t>Power Connection Port</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Electrical Connector</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -589,58 +621,79 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[1, 4]</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Described as the auxiliary port for powering the instrument, compatible with a C13 to 5-15 power cord.</t>
+        </is>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[1, 3, 8]</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>The enclosure is required by IEC 61010 to prevent access to hazardous voltages and parts, and is specifically relied upon to enclose hazardous circuitry. Its removal or modification would directly compromise user safety.</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.375</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>The power connection port interfaces with mains voltage and is required by IEC 61010 for safe connection and isolation. Any change or deletion could result in exposure to hazardous voltages.</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Power Switch</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Electrical Switch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -650,58 +703,79 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx; CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[1, 3]</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Switch that turns the instrument on and off.</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>90</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>[1, 3, 4, 7]</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>The power supply is required by the standard and is located in hazardous circuitry, as it interfaces with mains voltage and provides power to the system. Its compliance and integrity are essential for electrical safety.</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>The power switch is required by IEC 61010 for operator control and isolation from mains supply. It is located in hazardous (mains voltage) circuitry, and prevents access to hazardous energy by disconnecting power. It is relied upon for safe abnormal operation (e.g., emergency shutoff).</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power Cord (C13 to 5-15)</t>
+          <t>Front Panel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Device Panel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>low-medium</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -711,58 +785,85 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[1, 3, 4, 7]</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
+          <t>Exceptional performance – high cell viability and delivery efficiencies with decreased recovery and expansion times
+Simple, streamlined workflow —  easy to optimize and no need for cell concentration and buffer exchanges
+Operational and cell-friendly processing — no specific media, buffers, or chemical additives required
+Product Contents
+With the purchase of the Infinity MTx, CellFE provides the following products and accessories:
+System contents
+Optimizer kit contents
+Upon purchase of the Infinity MTx, users are asked to select an Optimizer Kit with sizes relevant to the cell types that will be used (see sizes below). Optimizer kits come with four MPAs. Once the desired MPA size is determined, users can purchase single-use MPAs of the correct size in packs of four. 
+Optimizer Kits
+System Components
+Infinity MTx device
+Front Panel
+User Interface Touchscreen – From here, the operator can detail and conduct the transfection processes, view and export information about previous transfection runs, change default system settings, and access additional information about operating the Infinity MTx. (See the software section of the manual for more information).
+Sample Loading Tray – Compatible with the Infinity MPA and Optimizer kit. Use the eject button on the touchscreen to open the tray. The MPA or Optimizer kit can be placed in the open tray by matching up the protrusion on the device with the recess on the tray.  WARNING:  Ensure nothing is touching the seam between the tray and the main body of the instrument, as this can damage the instrumentation and may cause harm to the user.
+Barcode Scanner – Located on the underside of the instrument above the tray. The barcode scanner reads the barcodes on the Infinity MPA package and saves device specific information to the notes section. Press the “Scan /Read ID” button to scan the barcode. 
+Back Panel
+Exhaust Air Vents – Used to vent air out of the instrument. CAUTION Do not block – Ensure at least 6” of clearan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Listed as a system component and described as part of the device interface.</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>90</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>[1, 4, 8]</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Power cord is required by IEC 61010, is part of hazardous (mains) circuitry, prevents access to live parts, and is relied upon for safe abnormal operation (e.g., cord integrity).</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.375</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>The front panel is a required enclosure component, providing physical separation between the user and internal hazardous circuitry. It prevents access to hazardous voltages and moving parts, and its removal or modification could result in exposure to electrical or mechanical hazards.</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power Connection Port</t>
+          <t>Compressed Air Inlet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Pneumatic Component</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>low-medium</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -772,58 +873,79 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[1, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Described as the primary attachment point for a pressurized air source, compatible with ¼” NPT Pressure line tubing and a push-to-connect fitting.</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>90</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[3, 8]</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Power connection port is required by IEC 61010 for safe connection to mains, is located in hazardous (mains) circuitry, and prevents direct access to hazardous voltages.</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.25</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>The compressed air inlet interfaces with hazardous pneumatic energy (up to 120 PSI) and improper connection or modification could result in hazardous conditions. IEC 61010 requires evaluation of components that interface with hazardous energy sources.</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Electrical Outlet</t>
+          <t>Exhaust Air Vents</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Ventilation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>low-medium</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -833,58 +955,85 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[1, 3]</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
+          <t>Exceptional performance – high cell viability and delivery efficiencies with decreased recovery and expansion times
+Simple, streamlined workflow —  easy to optimize and no need for cell concentration and buffer exchanges
+Operational and cell-friendly processing — no specific media, buffers, or chemical additives required
+Product Contents
+With the purchase of the Infinity MTx, CellFE provides the following products and accessories:
+System contents
+Optimizer kit contents
+Upon purchase of the Infinity MTx, users are asked to select an Optimizer Kit with sizes relevant to the cell types that will be used (see sizes below). Optimizer kits come with four MPAs. Once the desired MPA size is determined, users can purchase single-use MPAs of the correct size in packs of four. 
+Optimizer Kits
+System Components
+Infinity MTx device
+Front Panel
+User Interface Touchscreen – From here, the operator can detail and conduct the transfection processes, view and export information about previous transfection runs, change default system settings, and access additional information about operating the Infinity MTx. (See the software section of the manual for more information).
+Sample Loading Tray – Compatible with the Infinity MPA and Optimizer kit. Use the eject button on the touchscreen to open the tray. The MPA or Optimizer kit can be placed in the open tray by matching up the protrusion on the device with the recess on the tray.  WARNING:  Ensure nothing is touching the seam between the tray and the main body of the instrument, as this can damage the instrumentation and may cause harm to the user.
+Barcode Scanner – Located on the underside of the instrument above the tray. The barcode scanner reads the barcodes on the Infinity MPA package and saves device specific information to the notes section. Press the “Scan /Read ID” button to scan the barcode. 
+Back Panel
+Exhaust Air Vents – Used to vent air out of the instrument. CAUTION Do not block – Ensure at least 6” of clearan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Described as physical vents on the back panel for air exhaust.</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>[1, 4]</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.25</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Electrical outlets are required by IEC 61010 and are located in hazardous circuitry, making them critical for electrical safety compliance.</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>guide</t>
-        </is>
+          <t>Exhaust air vents are required by IEC 61010 for thermal management and enclosure ventilation. They also form part of the enclosure, preventing direct access to hazardous internal components.</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Connection Lines and Cables</t>
+          <t>Push-to-Connect Fitting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Pneumatic Connector</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>low-medium</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -894,42 +1043,403 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mentioned as the fitting used to connect tubing to the compressed air inlet.</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>[3, 8]</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>The push-to-connect fitting is relied upon to maintain a safe connection to hazardous pneumatic pressure. Failure or substitution could result in loss of containment and exposure to hazardous energy.</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>User Interface Touchscreen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Control Interface</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>guide</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
         </is>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>[3, 5]</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Exceptional performance – high cell viability and delivery efficiencies with decreased recovery and expansion times
+Simple, streamlined workflow —  easy to optimize and no need for cell concentration and buffer exchanges
+Operational and cell-friendly processing — no specific media, buffers, or chemical additives required
+Product Contents
+With the purchase of the Infinity MTx, CellFE provides the following products and accessories:
+System contents
+Optimizer kit contents
+Upon purchase of the Infinity MTx, users are asked to select an Optimizer Kit with sizes relevant to the cell types that will be used (see sizes below). Optimizer kits come with four MPAs. Once the desired MPA size is determined, users can purchase single-use MPAs of the correct size in packs of four. 
+Optimizer Kits
+System Components
+Infinity MTx device
+Front Panel
+User Interface Touchscreen – From here, the operator can detail and conduct the transfection processes, view and export information about previous transfection runs, change default system settings, and access additional information about operating the Infinity MTx. (See the software section of the manual for more information).
+Sample Loading Tray – Compatible with the Infinity MPA and Optimizer kit. Use the eject button on the touchscreen to open the tray. The MPA or Optimizer kit can be placed in the open tray by matching up the protrusion on the device with the recess on the tray.  WARNING:  Ensure nothing is touching the seam between the tray and the main body of the instrument, as this can damage the instrumentation and may cause harm to the user.
+Barcode Scanner – Located on the underside of the instrument above the tray. The barcode scanner reads the barcodes on the Infinity MPA package and saves device specific information to the notes section. Press the “Scan /Read ID” button to scan the barcode. 
+Back Panel
+Exhaust Air Vents – Used to vent air out of the instrument. CAUTION Do not block – Ensure at least 6” of clearan</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Described as a physical touchscreen for operator interaction and system control.</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[1, 7, 8]</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>The user interface touchscreen is required for safe operation and control of the device. It is relied upon for safe abnormal operation (e.g., emergency stop, system control) and its removal or malfunction could result in unsafe operation or inability to safely shut down the system.</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sample Loading Tray</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sample Handling</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>guide</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Exceptional performance – high cell viability and delivery efficiencies with decreased recovery and expansion times
+Simple, streamlined workflow —  easy to optimize and no need for cell concentration and buffer exchanges
+Operational and cell-friendly processing — no specific media, buffers, or chemical additives required
+Product Contents
+With the purchase of the Infinity MTx, CellFE provides the following products and accessories:
+System contents
+Optimizer kit contents
+Upon purchase of the Infinity MTx, users are asked to select an Optimizer Kit with sizes relevant to the cell types that will be used (see sizes below). Optimizer kits come with four MPAs. Once the desired MPA size is determined, users can purchase single-use MPAs of the correct size in packs of four. 
+Optimizer Kits
+System Components
+Infinity MTx device
+Front Panel
+User Interface Touchscreen – From here, the operator can detail and conduct the transfection processes, view and export information about previous transfection runs, change default system settings, and access additional information about operating the Infinity MTx. (See the software section of the manual for more information).
+Sample Loading Tray – Compatible with the Infinity MPA and Optimizer kit. Use the eject button on the touchscreen to open the tray. The MPA or Optimizer kit can be placed in the open tray by matching up the protrusion on the device with the recess on the tray.  WARNING:  Ensure nothing is touching the seam between the tray and the main body of the instrument, as this can damage the instrumentation and may cause harm to the user.
+Barcode Scanner – Located on the underside of the instrument above the tray. The barcode scanner reads the barcodes on the Infinity MPA package and saves device specific information to the notes section. Press the “Scan /Read ID” button to scan the barcode. 
+Back Panel
+Exhaust Air Vents – Used to vent air out of the instrument. CAUTION Do not block – Ensure at least 6” of clearan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Described as a physical tray for loading MPAs and Optimizer kits, with instructions for use.</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>[4, 5, 8]</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>The sample loading tray provides physical separation and access control to the sample chamber, which may be associated with hazardous moving parts or electrical circuitry. It maintains spacings and segregation, and its removal or improper use could result in exposure to hazards.</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Air Intake Fan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cooling Component</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>guide</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Provides cooling for internal electrical components and power supply.</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>[1, 7]</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N11" t="n">
         <v>0.25</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Connection lines and cables may be located in hazardous circuitry and are used to maintain spacings or segregation, both of which are critical per IEC 61010.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>The air intake fan is required to prevent overheating of internal electrical components, which could lead to fire or electrical hazards. IEC 61010 requires evaluation of cooling systems relied upon for safe abnormal operation.</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0.2 um Membrane Filters</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Filtration Component</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>guide</t>
         </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://stintertekesusdev.blob.core.windows.net/cdr-test/CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CellFE_Infinity_MTx_Operating_Manual.docx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ce behind instrument
+Compressed Air Inlet – The primary attachment point of the instrument –compatible with ¼” NPT Pressure line tubing fitted with a push to connect fitting. The instrument can be attached to a pressurized air source of 100 PSI for optimal functioning. The pressurized air may not exceed 120 PSI; the instrument can supply up to 80 PSI to liquid samples, but only if hooked up to a pressure source of 100 – 105 PSI. 
+Connecting the tubing: Ensure the air source is turned off and decompressed. Gently push the push-to-connect fitting into the compressed air inlet of the instrument. 
+Disconnecting the tubing: turn off the instrument and shut off the air source. Ensure both systems are decompressed before removing the tubing by pushing the small tab located on the instrument’s compressed air inlet.
+Air Intake Fan – Provides cooling for internal electrical components and power supply. CAUTION Do not block – Ensure at least 6” of clearance behind instrument
+Power Connection Port – Auxiliary port that powers the instrument. The C13 to 5-15 power cord can be plugged directly into the Infinity MTx, with the opposing 3-prong end able to connect to a properly grounded 3-prong, 110-120V/50-60Hz power source. 
+Power Switch – Switch that turns the instrument on and off. Electrical supply is limited by the power switch, and after operation it is best to shut the instrument off. 
+USB-A Connection Port – An auxiliary port that a USB type A can be attached to. Used to export data. This data export process is detailed in the software section.
+LAN Connection Port – An auxiliary port that a LAN cable can be connected to. For current customer use, the instrument does not have internet connection capabilities.
+Infinity MPA 
+MPA Lid – Attached via a hinge to the collection chamber lid. Once samples are loaded into the sample chambers, the lid can be closed by pushing down until the lid latch is locked in place. Once closed, the 0.2 um membrane filters located on the air inle</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Located on the air inlet, as mentioned in the context of the MPA lid.</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>[3, 4]</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>The 0.2 um membrane filters are located on the air inlet, which interfaces with pressurized air (up to 120 PSI). This is hazardous circuitry per IEC 61010, and the filter acts as a barrier to prevent ingress of contaminants and possible exposure to hazardous pressure. It also encloses/prevents direct access to hazardous air flow.</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
